--- a/Q1_结果.xlsx
+++ b/Q1_结果.xlsx
@@ -12,7 +12,7 @@
     <sheet name="余量敏感性" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q1_单点组批'!$A$1:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q1_单点组批'!$A$1:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'机型最大安全载荷'!$A$1:$E$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'余量敏感性'!$A$1:$H$4</definedName>
   </definedNames>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,23 +487,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S001-FOD-01,S001-FOD-02,S001-HYG-01,S001-WAT-01,S001-WAT-02,S001-WAT-03,S001-WAT-04</t>
+          <t>S001-HYG-01,S001-WAT-01,S001-WAT-02,S001-WAT-03,S001-WAT-04,S001-WAT-05</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
-        <v>0.199</v>
+        <v>0.17</v>
       </c>
       <c r="G2" t="n">
-        <v>1561.426741698545</v>
+        <v>1495.426741698547</v>
       </c>
       <c r="H2" t="n">
-        <v>3.031909089609001</v>
+        <v>2.92627284583651</v>
       </c>
       <c r="I2" t="n">
-        <v>62.10113637988749</v>
+        <v>63.42158942704362</v>
       </c>
     </row>
     <row r="3">
@@ -524,23 +524,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S001-MED-01,S001-MED-02,S001-FOD-03,S001-HYG-02,S001-WAT-05,S001-WAT-06,S001-WAT-07,S001-WAT-08</t>
+          <t>S001-MED-01,S001-MED-02,S001-FOD-01,S001-FOD-02,S001-FOD-03,S001-HYG-02,S001-WAT-06,S001-WAT-07,S001-WAT-08</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>0.195</v>
+        <v>0.224</v>
       </c>
       <c r="G3" t="n">
-        <v>1627.426741698545</v>
+        <v>1693.426741698547</v>
       </c>
       <c r="H3" t="n">
-        <v>2.976120742060993</v>
+        <v>3.004697890001106</v>
       </c>
       <c r="I3" t="n">
-        <v>62.79849072423757</v>
+        <v>62.44127637498617</v>
       </c>
     </row>
     <row r="4">
@@ -571,13 +571,13 @@
         <v>0.067</v>
       </c>
       <c r="G4" t="n">
-        <v>1819.890041865775</v>
+        <v>1819.890041865742</v>
       </c>
       <c r="H4" t="n">
-        <v>2.798212858714521</v>
+        <v>2.721926619516321</v>
       </c>
       <c r="I4" t="n">
-        <v>30.04467853213697</v>
+        <v>31.95183451209197</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>0.144</v>
       </c>
       <c r="G5" t="n">
-        <v>2045.008126582572</v>
+        <v>2045.008126582539</v>
       </c>
       <c r="H5" t="n">
-        <v>6.069552815881007</v>
+        <v>5.739371179997408</v>
       </c>
       <c r="I5" t="n">
-        <v>24.13058980148741</v>
+        <v>28.2578602500324</v>
       </c>
     </row>
     <row r="6">
@@ -645,13 +645,13 @@
         <v>0.067</v>
       </c>
       <c r="G6" t="n">
-        <v>2080.242812051235</v>
+        <v>2080.242812051228</v>
       </c>
       <c r="H6" t="n">
-        <v>2.853669949807178</v>
+        <v>2.779171039452936</v>
       </c>
       <c r="I6" t="n">
-        <v>28.65825125482056</v>
+        <v>30.5207240136766</v>
       </c>
     </row>
     <row r="7">
@@ -682,13 +682,13 @@
         <v>0.144</v>
       </c>
       <c r="G7" t="n">
-        <v>2369.810858112433</v>
+        <v>2369.810858112426</v>
       </c>
       <c r="H7" t="n">
-        <v>6.085818119129948</v>
+        <v>5.763372389063068</v>
       </c>
       <c r="I7" t="n">
-        <v>23.92727351087565</v>
+        <v>27.95784513671165</v>
       </c>
     </row>
     <row r="8">
@@ -704,28 +704,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S004-HYG-01,S004-WAT-01</t>
+          <t>S004-MED-01,S004-FOD-01,S004-HYG-01,S004-WAT-01,S004-WAT-02,S004-WAT-03</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>0.062</v>
+        <v>0.156</v>
       </c>
       <c r="G8" t="n">
-        <v>1925.7724360479</v>
+        <v>2305.185491467791</v>
       </c>
       <c r="H8" t="n">
-        <v>2.784494734796808</v>
+        <v>6.17691902989136</v>
       </c>
       <c r="I8" t="n">
-        <v>30.38763163007979</v>
+        <v>22.788512126358</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +736,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -746,23 +746,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S004-MED-01,S004-FOD-01,S004-WAT-02,S004-WAT-03</t>
+          <t>S005-MED-01,S005-FOD-01,S005-HYG-01,S005-WAT-01,S005-WAT-02,S005-WAT-03</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>0.094</v>
+        <v>0.156</v>
       </c>
       <c r="G9" t="n">
-        <v>2173.185491467822</v>
+        <v>1880.045617096052</v>
       </c>
       <c r="H9" t="n">
-        <v>5.771310040262703</v>
+        <v>4.23878004069446</v>
       </c>
       <c r="I9" t="n">
-        <v>27.85862449671621</v>
+        <v>47.01524949131925</v>
       </c>
     </row>
     <row r="10">
@@ -773,7 +773,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>S005-MED-01,S005-FOD-01,S005-HYG-01,S005-WAT-01,S005-WAT-02,S005-WAT-03</t>
+          <t>S006-MED-01,S006-FOD-01,S006-HYG-01,S006-WAT-01,S006-WAT-02,S006-WAT-03</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -793,13 +793,13 @@
         <v>0.156</v>
       </c>
       <c r="G10" t="n">
-        <v>1880.04561709608</v>
+        <v>1560.863885273963</v>
       </c>
       <c r="H10" t="n">
-        <v>4.469072265539761</v>
+        <v>2.593979284603349</v>
       </c>
       <c r="I10" t="n">
-        <v>44.13659668075298</v>
+        <v>67.57525894245813</v>
       </c>
     </row>
     <row r="11">
@@ -810,7 +810,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -820,23 +820,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S006-MED-01,S006-FOD-01,S006-HYG-01,S006-WAT-01,S006-WAT-02,S006-WAT-03</t>
+          <t>S007-MED-01,S007-FOD-01,S007-HYG-01,S007-WAT-01,S007-WAT-02</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>0.156</v>
+        <v>0.129</v>
       </c>
       <c r="G11" t="n">
-        <v>1560.863885273963</v>
+        <v>1907.482101486218</v>
       </c>
       <c r="H11" t="n">
-        <v>2.732146854650995</v>
+        <v>3.410447825860139</v>
       </c>
       <c r="I11" t="n">
-        <v>65.84816431686255</v>
+        <v>57.36940217674827</v>
       </c>
     </row>
     <row r="12">
@@ -847,7 +847,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>S007-MED-01,S007-FOD-01,S007-HYG-01,S007-WAT-01,S007-WAT-02</t>
+          <t>S008-MED-01,S008-FOD-01,S008-HYG-01,S008-WAT-01,S008-WAT-02</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -867,13 +867,13 @@
         <v>0.129</v>
       </c>
       <c r="G12" t="n">
-        <v>1907.482101486225</v>
+        <v>2203.759889419427</v>
       </c>
       <c r="H12" t="n">
-        <v>3.606515762629472</v>
+        <v>5.857497107796528</v>
       </c>
       <c r="I12" t="n">
-        <v>54.9185529671316</v>
+        <v>26.78128615254341</v>
       </c>
     </row>
     <row r="13">
@@ -884,33 +884,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S008-MED-01,S008-FOD-01,S008-HYG-01,S008-WAT-01,S008-WAT-02</t>
+          <t>S009-MED-01,S009-FOD-01,S009-WAT-01</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
-        <v>0.129</v>
+        <v>0.067</v>
       </c>
       <c r="G13" t="n">
-        <v>2203.759889419462</v>
+        <v>1560.77979054711</v>
       </c>
       <c r="H13" t="n">
-        <v>6.208195835545198</v>
+        <v>2.102455644233721</v>
       </c>
       <c r="I13" t="n">
-        <v>22.39755205568502</v>
+        <v>47.43860889415698</v>
       </c>
     </row>
     <row r="14">
@@ -921,7 +921,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S009-MED-01,S009-FOD-01,S009-WAT-01</t>
+          <t>S010-MED-01,S010-FOD-01,S010-WAT-01</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -941,13 +941,13 @@
         <v>0.067</v>
       </c>
       <c r="G14" t="n">
-        <v>1560.779790547111</v>
+        <v>1554.572239161442</v>
       </c>
       <c r="H14" t="n">
-        <v>2.161170561805989</v>
+        <v>1.821047284796383</v>
       </c>
       <c r="I14" t="n">
-        <v>45.97073595485027</v>
+        <v>54.47381788009044</v>
       </c>
     </row>
     <row r="15">
@@ -958,7 +958,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S010-MED-01,S010-FOD-01,S010-WAT-01</t>
+          <t>S011-MED-01,S011-FOD-01,S011-WAT-01</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -978,13 +978,13 @@
         <v>0.067</v>
       </c>
       <c r="G15" t="n">
-        <v>1554.57223916144</v>
+        <v>1189.630804564486</v>
       </c>
       <c r="H15" t="n">
-        <v>1.870074259163209</v>
+        <v>1.077172635206365</v>
       </c>
       <c r="I15" t="n">
-        <v>53.24814352091978</v>
+        <v>73.07068411984088</v>
       </c>
     </row>
     <row r="16">
@@ -995,7 +995,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S011-MED-01,S011-FOD-01,S011-WAT-01</t>
+          <t>S012-MED-01,S012-FOD-01,S012-WAT-01</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1015,13 +1015,13 @@
         <v>0.067</v>
       </c>
       <c r="G16" t="n">
-        <v>1186.678806680367</v>
+        <v>1923.801400652118</v>
       </c>
       <c r="H16" t="n">
-        <v>1.104895989334446</v>
+        <v>2.755237906410221</v>
       </c>
       <c r="I16" t="n">
-        <v>72.37760026663884</v>
+        <v>31.11905233974447</v>
       </c>
     </row>
     <row r="17">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S012-MED-01,S012-FOD-01,S012-WAT-01</t>
+          <t>S013-MED-01,S013-FOD-01,S013-WAT-01</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1052,13 +1052,13 @@
         <v>0.067</v>
       </c>
       <c r="G17" t="n">
-        <v>1923.801400652132</v>
+        <v>1510.400941459331</v>
       </c>
       <c r="H17" t="n">
-        <v>2.831146279114181</v>
+        <v>1.82456931010719</v>
       </c>
       <c r="I17" t="n">
-        <v>29.22134302214548</v>
+        <v>54.38576724732024</v>
       </c>
     </row>
     <row r="18">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>S013-MED-01,S013-FOD-01,S013-WAT-01</t>
+          <t>S014-MED-01,S014-FOD-01,S014-WAT-01</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1089,13 +1089,13 @@
         <v>0.067</v>
       </c>
       <c r="G18" t="n">
-        <v>1510.400941459339</v>
+        <v>1868.598447869045</v>
       </c>
       <c r="H18" t="n">
-        <v>1.874317227563748</v>
+        <v>2.137306960043424</v>
       </c>
       <c r="I18" t="n">
-        <v>53.1420693109063</v>
+        <v>46.56732599891439</v>
       </c>
     </row>
     <row r="19">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>S014-MED-01,S014-FOD-01,S014-WAT-01</t>
+          <t>S015-MED-01,S015-FOD-01,S015-WAT-01</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1126,54 +1126,17 @@
         <v>0.067</v>
       </c>
       <c r="G19" t="n">
-        <v>1868.598447869042</v>
+        <v>1829.574101016009</v>
       </c>
       <c r="H19" t="n">
-        <v>2.192823174361967</v>
+        <v>2.310905562967101</v>
       </c>
       <c r="I19" t="n">
-        <v>45.17942064095083</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Q1-019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S015</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>S015-MED-01,S015-FOD-01,S015-WAT-01</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>25</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1829.574101016016</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.372661900043978</v>
-      </c>
-      <c r="I20" t="n">
-        <v>40.68345249890055</v>
+        <v>42.22736092582247</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I20"/>
+  <autoFilter ref="A1:I19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1334,7 +1297,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.57274508166716</v>
+        <v>78.36808429029418</v>
       </c>
       <c r="E7" t="n">
         <v>308.9542541503906</v>
@@ -1397,7 +1360,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>77.41280754322531</v>
+        <v>78.25159798584195</v>
       </c>
       <c r="E10" t="n">
         <v>561.8041381835938</v>
@@ -1460,7 +1423,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>72.03567151642432</v>
+        <v>74.56856928385008</v>
       </c>
       <c r="E13" t="n">
         <v>398.2391662597656</v>
@@ -1712,7 +1675,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>67.10627219580175</v>
+        <v>71.10795458110545</v>
       </c>
       <c r="E25" t="n">
         <v>372.9093322753906</v>
@@ -1862,7 +1825,7 @@
         <v>24.99999999999991</v>
       </c>
       <c r="E32" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="33">
@@ -1883,7 +1846,7 @@
         <v>29.99999999999989</v>
       </c>
       <c r="E33" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="34">
@@ -1904,7 +1867,7 @@
         <v>79.99999999999972</v>
       </c>
       <c r="E34" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="35">
@@ -1964,7 +1927,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>77.0579541035849</v>
+        <v>78.0158420994357</v>
       </c>
       <c r="E37" t="n">
         <v>413.3009948730469</v>
@@ -2279,7 +2242,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>63.53350011124661</v>
+        <v>68.55368563530988</v>
       </c>
       <c r="E52" t="n">
         <v>308.9542541503906</v>
@@ -2342,7 +2305,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>63.19878654700716</v>
+        <v>68.2339752221057</v>
       </c>
       <c r="E55" t="n">
         <v>561.8041381835938</v>
@@ -2405,7 +2368,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>56.41926603484819</v>
+        <v>63.25821420703704</v>
       </c>
       <c r="E58" t="n">
         <v>398.2391662597656</v>
@@ -2636,7 +2599,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>27.98450000720898</v>
+        <v>28.63189320883539</v>
       </c>
       <c r="E69" t="n">
         <v>372.9093322753906</v>
@@ -2657,7 +2620,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>50.14314849019286</v>
+        <v>58.4348388882438</v>
       </c>
       <c r="E70" t="n">
         <v>372.9093322753906</v>
@@ -2807,7 +2770,7 @@
         <v>24.99999999999991</v>
       </c>
       <c r="E77" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="78">
@@ -2828,7 +2791,7 @@
         <v>29.99999999999989</v>
       </c>
       <c r="E78" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="79">
@@ -2849,7 +2812,7 @@
         <v>79.99999999999972</v>
       </c>
       <c r="E79" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="80">
@@ -2909,7 +2872,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>62.83371237100909</v>
+        <v>68.01369624507714</v>
       </c>
       <c r="E82" t="n">
         <v>413.3009948730469</v>
@@ -3203,7 +3166,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>25.0477306709336</v>
+        <v>26.58002564428624</v>
       </c>
       <c r="E96" t="n">
         <v>308.9542541503906</v>
@@ -3224,7 +3187,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>42.72676498330469</v>
+        <v>52.48017635631896</v>
       </c>
       <c r="E97" t="n">
         <v>308.9542541503906</v>
@@ -3245,7 +3208,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>24.66656278775963</v>
+        <v>24.77018526950108</v>
       </c>
       <c r="E98" t="n">
         <v>561.8041381835938</v>
@@ -3266,7 +3229,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>23.52398390570631</v>
+        <v>25.44226417400452</v>
       </c>
       <c r="E99" t="n">
         <v>561.8041381835938</v>
@@ -3287,7 +3250,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>42.26595467938921</v>
+        <v>51.83788025422388</v>
       </c>
       <c r="E100" t="n">
         <v>561.8041381835938</v>
@@ -3308,7 +3271,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>17.49881499924575</v>
+        <v>19.60098964626233</v>
       </c>
       <c r="E101" t="n">
         <v>398.2391662597656</v>
@@ -3329,7 +3292,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>20.47993780821898</v>
+        <v>23.19235724395682</v>
       </c>
       <c r="E102" t="n">
         <v>398.2391662597656</v>
@@ -3350,7 +3313,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>33.09447541822266</v>
+        <v>44.0357282335853</v>
       </c>
       <c r="E103" t="n">
         <v>398.2391662597656</v>
@@ -3560,7 +3523,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.16205884078856</v>
+        <v>13.51478106915183</v>
       </c>
       <c r="E113" t="n">
         <v>372.9093322753906</v>
@@ -3581,7 +3544,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>17.34082667319623</v>
+        <v>20.7307424193294</v>
       </c>
       <c r="E114" t="n">
         <v>372.9093322753906</v>
@@ -3602,7 +3565,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>24.58936030019458</v>
+        <v>35.99921043135708</v>
       </c>
       <c r="E115" t="n">
         <v>372.9093322753906</v>
@@ -3665,7 +3628,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>78.42622505207288</v>
+        <v>78.94325749563535</v>
       </c>
       <c r="E118" t="n">
         <v>293.2289123535156</v>
@@ -3752,7 +3715,7 @@
         <v>24.99999999999991</v>
       </c>
       <c r="E122" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="123">
@@ -3773,7 +3736,7 @@
         <v>29.99999999999989</v>
       </c>
       <c r="E123" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="124">
@@ -3794,7 +3757,7 @@
         <v>79.99999999999972</v>
       </c>
       <c r="E124" t="n">
-        <v>293.3490295410156</v>
+        <v>295.3617553710938</v>
       </c>
     </row>
     <row r="125">
@@ -3833,7 +3796,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>24.15694629996786</v>
+        <v>25.92680216904512</v>
       </c>
       <c r="E126" t="n">
         <v>413.3009948730469</v>
@@ -3854,7 +3817,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>41.7949329452793</v>
+        <v>51.59639254783173</v>
       </c>
       <c r="E127" t="n">
         <v>413.3009948730469</v>
@@ -4043,7 +4006,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>69.6755165950637</v>
+        <v>72.87469880141401</v>
       </c>
       <c r="E136" t="n">
         <v>571.7992553710938</v>
@@ -4119,10 +4082,10 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>61.75165407354247</v>
+        <v>59.24113055647759</v>
       </c>
       <c r="E2" t="n">
-        <v>32795.5480341381</v>
+        <v>32798.50003202202</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -4144,19 +4107,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>63.7941084600151</v>
+        <v>59.24113055647759</v>
       </c>
       <c r="E3" t="n">
-        <v>34589.320470186</v>
+        <v>32798.50003202202</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
         <v>9</v>
@@ -4175,19 +4138,19 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>77.8077672927791</v>
+        <v>67.3586560187448</v>
       </c>
       <c r="E4" t="n">
-        <v>36947.02987742773</v>
+        <v>36616.84871084218</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
